--- a/AAII_Financials/Quarterly/TMSNY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TMSNY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="92">
   <si>
     <t>TMSNY</t>
   </si>
@@ -656,79 +656,83 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -768,8 +772,11 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -809,8 +816,11 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -850,8 +860,11 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -867,8 +880,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -908,8 +922,11 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -949,8 +966,11 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -990,8 +1010,11 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1031,8 +1054,11 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,8 +1071,9 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1086,8 +1113,11 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1127,8 +1157,11 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1144,8 +1177,9 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1185,8 +1219,11 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1226,8 +1263,11 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1267,8 +1307,11 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1308,8 +1351,11 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1349,8 +1395,11 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1390,8 +1439,11 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1431,8 +1483,11 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1472,8 +1527,11 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1513,8 +1571,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1554,8 +1615,11 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1595,8 +1659,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1636,8 +1703,11 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1677,8 +1747,11 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1718,8 +1791,11 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1759,8 +1835,11 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1800,54 +1879,60 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1863,8 +1948,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1880,131 +1966,141 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>150800</v>
+      </c>
+      <c r="E41" s="3">
         <v>203500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>305400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>114200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>193900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>106900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>100900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>89900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>105700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>87000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>100900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>112100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>89900</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>45800</v>
+      </c>
+      <c r="E42" s="3">
         <v>42600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>64700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>56200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>52800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>69800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>57800</v>
-      </c>
-      <c r="J42" s="3">
-        <v>35100</v>
       </c>
       <c r="K42" s="3">
         <v>35100</v>
       </c>
       <c r="L42" s="3">
-        <v>0</v>
+        <v>35100</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>57800</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>35100</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>251500</v>
+      </c>
+      <c r="E43" s="3">
         <v>248000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>242300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>231500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>259600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>286200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>292600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>313500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>321300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>353700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>292600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>337000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>313500</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2044,8 +2140,11 @@
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2055,12 +2154,12 @@
       <c r="E45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3">
         <v>235300</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H45" s="3" t="s">
         <v>4</v>
       </c>
@@ -2085,172 +2184,187 @@
       <c r="O45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>448100</v>
+      </c>
+      <c r="E46" s="3">
         <v>494100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>612300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>637100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>506300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>462900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>451300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>438500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>462100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>440700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>451300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>449000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>438500</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>28900</v>
+      </c>
+      <c r="E47" s="3">
         <v>35200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>52000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>17100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>14500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>21800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>27500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>42900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>7000</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N47" s="3">
         <v>27500</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P47" s="3">
         <v>42900</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E48" s="3">
         <v>46000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>50200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>50800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>57800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>58000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>58100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>63100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>63700</v>
-      </c>
-      <c r="L48" s="3">
-        <v>58100</v>
       </c>
       <c r="M48" s="3">
         <v>58100</v>
       </c>
       <c r="N48" s="3">
+        <v>58100</v>
+      </c>
+      <c r="O48" s="3">
         <v>62900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>63100</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1259900</v>
+      </c>
+      <c r="E49" s="3">
         <v>1277800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1300400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1280900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1496000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1523600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1529800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1538800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1540500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1506200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1529800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1537000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1538800</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2290,8 +2404,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2331,8 +2448,11 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2360,20 +2480,23 @@
       <c r="K52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M52" s="3">
         <v>34200</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N52" s="3">
+      <c r="N52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O52" s="3">
         <v>64800</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2413,49 +2536,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2199000</v>
+      </c>
+      <c r="E54" s="3">
         <v>2249300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2388600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2276700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2331600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2326800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2236600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2231800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2168700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2202200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2236600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2250200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2231800</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2471,8 +2600,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2488,254 +2618,273 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>252700</v>
+      </c>
+      <c r="E57" s="3">
         <v>54000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>243100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>51100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>213900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>23900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>175900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>42200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>183400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>182000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>175900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>195100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>42200</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E58" s="3">
         <v>16900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>297100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>257200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>20000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>195000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>378900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>204100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>18200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>374900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>378900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>209700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>204100</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>610500</v>
+      </c>
+      <c r="E59" s="3">
         <v>621300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>611500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>631400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>511000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>583900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>523600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>567000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>470900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>505100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>523600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>504500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>567000</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>880000</v>
+      </c>
+      <c r="E60" s="3">
         <v>850400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1151700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1073400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>744800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>943400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1078400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>919500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>672500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1062000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1078400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>909300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>919500</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>825400</v>
+      </c>
+      <c r="E61" s="3">
         <v>792100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>590600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>469600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>745800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>569700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>494000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>636700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>880900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>451600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>494000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>631800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>636700</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E62" s="3">
         <v>17600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>21900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2300</v>
-      </c>
-      <c r="M62" s="3">
-        <v>3600</v>
       </c>
       <c r="N62" s="3">
         <v>3600</v>
       </c>
       <c r="O62" s="3">
+        <v>3600</v>
+      </c>
+      <c r="P62" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2775,8 +2924,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2816,8 +2968,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2857,49 +3012,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1827000</v>
+      </c>
+      <c r="E66" s="3">
         <v>1771300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1854900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1637700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1633300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1644900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1691900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1653400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1675700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1632500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1691900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1662300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1653400</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2915,8 +3076,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2956,8 +3118,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2997,8 +3162,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3038,8 +3206,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3079,49 +3250,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1421100</v>
+      </c>
+      <c r="E72" s="3">
         <v>1430300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1343300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1258000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1152300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1179800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1103900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1137500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1074800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1125800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1103900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1153800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1137500</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3161,8 +3338,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3202,8 +3382,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3243,49 +3426,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>372000</v>
+      </c>
+      <c r="E76" s="3">
         <v>478000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>533700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>639000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>698300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>682000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>544800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>578400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>493000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>569700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>544800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>587800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>578400</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3325,54 +3514,60 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3412,8 +3607,11 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3429,49 +3627,53 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E83" s="3">
         <v>-58600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>21600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>-64300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>23900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>-60600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>23200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>-56800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>20800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>22900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>23900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>23500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>-60600</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3511,8 +3713,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3552,8 +3757,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3593,8 +3801,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3634,8 +3845,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3675,49 +3889,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>104900</v>
+      </c>
+      <c r="E89" s="3">
         <v>152000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>72700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>159500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>92500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>137300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>83700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>129000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>81400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>48900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>83700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>61100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>129000</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3733,49 +3953,53 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4000</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-2000</v>
       </c>
       <c r="J91" s="3">
         <v>-2000</v>
       </c>
       <c r="K91" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="L91" s="3">
         <v>-8100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3815,8 +4039,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3856,49 +4083,55 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-25200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>289400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-15200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-16100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-19700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-21800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-31500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-39800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-20300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-21800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-22400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-31500</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3914,49 +4147,53 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>117900</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>110500</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>96900</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>88300</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L96" s="3">
         <v>74400</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N96" s="3">
         <v>88300</v>
       </c>
-      <c r="N96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3996,8 +4233,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4037,8 +4277,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4078,127 +4321,139 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-70300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-107600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-210000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-134300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-184200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-104000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-74200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-82800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-31300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-41000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-74200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-16400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-82800</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E101" s="3">
         <v>6300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E102" s="3">
         <v>19300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>170800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>6900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-108500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>19900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-11200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>16500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>9500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-13900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-11200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>22100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>16500</v>
       </c>
     </row>
